--- a/Report/ReportDelete.xlsx
+++ b/Report/ReportDelete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ppham\Documents\Do an\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0466BA0E-E201-461B-BC78-CF0F0B208BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5957C08-4B6E-443A-8D9F-1BA0D260897F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,10 +514,11 @@
     <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="25.109375" customWidth="1"/>
     <col min="5" max="5" width="14.21875" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="19.5546875" customWidth="1"/>
     <col min="8" max="8" width="12.21875" customWidth="1"/>
     <col min="9" max="9" width="29.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.3">
